--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2024_aysen.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2024_aysen.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29 11:18</t>
+    <t xml:space="preserve">2026-08-19 15:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2024_aysen.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2024_aysen.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 15:12</t>
+    <t xml:space="preserve">2026-08-28 15:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -631,7 +631,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>25.94</v>
+        <v>85.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2024_aysen.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2024_aysen.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:07</t>
+    <t xml:space="preserve">2026-08-29 05:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,13 +474,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>44.62</v>
+        <v>89.23</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>42.18</v>
+        <v>84.37</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2.43</v>
+        <v>4.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2024_aysen.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2024_aysen.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:44</t>
+    <t xml:space="preserve">2026-09-07 11:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
